--- a/神社檔案/官社_鄉社前8.xlsx
+++ b/神社檔案/官社_鄉社前8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林芷葳\Documents\GitHub\mapu2\神社檔案\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CB87FB3-7F7E-4067-A748-BF37A06F68A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D180426-B011-45E2-82E1-C2693D34AC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>臺南市新營區信義街73號</t>
   </si>
   <si>
-    <t>1937年設立、同年11月27日鎮座，社格鄉社（1942年列格）。戰後改為中山公園與忠烈祠，1976年為興建新營醫院遷往新化虎頭埤，原址即今衛福部新營醫院；原神馬像現存於新營區。</t>
-  </si>
-  <si>
     <t>清水神社</t>
   </si>
   <si>
@@ -148,9 +145,6 @@
     <t>臺南市中西區忠義路二段1號（南美館2館）</t>
   </si>
   <si>
-    <t>前身為1901年北白川宮御遺跡所，1920年動工、1923年完工、同年10月28日鎮座，1925年列官幣中社，為台灣唯二官幣社之一（社格僅次於台灣神宮）。主祭北白川宮能久親王。戰後改忠烈祠，1969年拆除；內苑原址今為臺南市美術館2館，外苑今為忠義國小。</t>
-  </si>
-  <si>
     <t>新竹神社</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
   </si>
   <si>
     <t>臺中市北區雙十路一段（台中公園內）</t>
-  </si>
-  <si>
-    <t>第一代神社1912年落成、同年12月17日鎮座，1913年升縣社，位於台中公園。因蟻害與都市發展，1942年遷建至東北方水源地（新高町），升國幣小社。戰後第二代神社改忠烈祠、1970年代拆除改建，今為台中市忠烈祠與孔廟；台中公園內仍存第一代神社之鳥居、狛犬、銅馬、石橋與石燈籠基座等遺跡。</t>
   </si>
   <si>
     <t>嘉義神社</t>
@@ -192,6 +183,408 @@
   </si>
   <si>
     <t>經度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>前身為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1901</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年北白川宮御遺跡所，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1920</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年動工、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1923</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年完工、同年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日鎮座，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1925</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年列官幣中社，為台灣唯二官幣社之一（社格僅次於台灣神宮）。主祭北白川宮能久親王。戰後改忠烈祠，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1969</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年拆除；內苑原址今為臺南市美術館</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>館，外苑今為忠義國小。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>第一代神社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1912</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年落成、同年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日鎮座，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1913</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年升縣社，位於台中公園。因蟻害與都市發展，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1942</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年遷建至東北方水源地（新高町），升國幣小社。戰後第二代神社改忠烈祠、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1970</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年代拆除改建，今為台中市忠烈祠與孔廟；台中公園內仍存第一代神社之鳥居、狛犬、銅馬、石橋與石燈籠基座等遺跡。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1937</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年設立、同年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日鎮座，社格鄉社（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1942</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年列格）。戰後改為中山公園與忠烈祠，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體-ExtB"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>1976</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年為興建新營醫院遷往新化虎頭埤，原址即今衛福部新營醫院；原神馬像現存於新營區。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -199,7 +592,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +647,20 @@
       <name val="Microsoft JhengHei"/>
       <family val="4"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="細明體-ExtB"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BiauKaiTC Regular"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -275,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -288,6 +695,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -616,10 +1024,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -799,7 +1207,7 @@
         <v>1931</v>
       </c>
       <c r="H7" s="2">
-        <v>1945</v>
+        <v>1960</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>30</v>
@@ -828,10 +1236,10 @@
         <v>1937</v>
       </c>
       <c r="H8" s="2">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" customHeight="1">
@@ -839,13 +1247,13 @@
         <v>108</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="E9" s="6">
         <v>24.270628897396062</v>
@@ -860,7 +1268,7 @@
         <v>1945</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16.2" customHeight="1">
@@ -868,13 +1276,13 @@
         <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="E10" s="5">
         <v>22.9895</v>
@@ -888,8 +1296,8 @@
       <c r="H10" s="2">
         <v>1945</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>42</v>
+      <c r="I10" s="8" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16.2" customHeight="1">
@@ -897,13 +1305,13 @@
         <v>110</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E11" s="5">
         <v>24.794180000000001</v>
@@ -918,7 +1326,7 @@
         <v>1945</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16.2" customHeight="1">
@@ -926,13 +1334,13 @@
         <v>111</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E12" s="5">
         <v>24.145697486523598</v>
@@ -944,10 +1352,10 @@
         <v>1912</v>
       </c>
       <c r="H12" s="2">
-        <v>1945</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>50</v>
+        <v>1946</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.2" customHeight="1">
@@ -955,13 +1363,13 @@
         <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E13" s="6">
         <v>23.483174657139589</v>
@@ -973,10 +1381,10 @@
         <v>1915</v>
       </c>
       <c r="H13" s="2">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/神社檔案/官社_鄉社前8.xlsx
+++ b/神社檔案/官社_鄉社前8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林芷葳\Documents\GitHub\mapu2\神社檔案\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaish_mac/Desktop/DRHS/for github/mapu2/神社檔案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D180426-B011-45E2-82E1-C2693D34AC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46EF0D-2A10-A146-A089-E66E783AF941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="神社資料" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>編號</t>
   </si>
@@ -586,13 +586,158 @@
       <t>年為興建新營醫院遷往新化虎頭埤，原址即今衛福部新營醫院；原神馬像現存於新營區。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳳山神社</t>
+  </si>
+  <si>
+    <t>鳳山醫院</t>
+  </si>
+  <si>
+    <t>高雄市鳳山區新興里經武路42號42之1號</t>
+  </si>
+  <si>
+    <t>鳳山神社由鳳山郡各界於1933年起籌建，1935年完成並舉行鎮座祭，1943年升格為鄉社。戰後神社建物一度作為衛生院與醫療設施使用，後續陸續拆除，原址興建鳳山醫院。現今僅存部分石垣遺構，部分狛犬、石燈籠與相關構件則散置於鳳山地區其他廟宇與紀念設施。</t>
+  </si>
+  <si>
+    <t>新莊神社</t>
+  </si>
+  <si>
+    <t>和泰汽車新莊綜合園區</t>
+  </si>
+  <si>
+    <t>新北市新莊區思源里明中街10號</t>
+  </si>
+  <si>
+    <t>新莊神社於1935年開始規劃興建，1937年鎮座啟用，主祀明治天皇、倉稻魂大神與北白川宮能久親王，1944年升格為鄉社。戰後神社遭拆除，土地先後作為血清研究所及和泰汽車廠區使用，目前園區內已不見神社建築，但部分狛犬、石燈籠與神轎仍保存於新莊地藏庵。</t>
+  </si>
+  <si>
+    <t>豐原神社</t>
+  </si>
+  <si>
+    <t>南陽國小</t>
+  </si>
+  <si>
+    <t>臺中市豐原區中陽里南陽路440號</t>
+  </si>
+  <si>
+    <t>豐原神社位於豐原街下南坑，1936年鎮座，原為無格社，1944年升格為鄉社。主祭神包括天照大神及開拓三神等。戰後神社用地改建為南陽國小，部分狛犬與石燈籠被移置至地方福德祠保存。</t>
+  </si>
+  <si>
+    <t>曾文神社</t>
+  </si>
+  <si>
+    <t>警察廣播電臺臺南分臺、民宅、農地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">臺南市麻豆區南勢里85號-21 </t>
+  </si>
+  <si>
+    <t>曾文神社由地方人士於1936年發起興建，1938年完工啟用，是曾文郡規模最大的神社，1944年升格為鄉社。神社除宗教功能外，也經常舉辦運動會、武道與遊行活動。戰後園區改為中山公園並曾遭軍方使用，現址分布有警察廣播電臺、民宅與農地。</t>
+  </si>
+  <si>
+    <t>東石神社</t>
+  </si>
+  <si>
+    <t>朴子藝術公園</t>
+  </si>
+  <si>
+    <t>嘉義縣朴子市安福里山通路2之9號</t>
+  </si>
+  <si>
+    <t>東石神社位於朴子市區東側，1936年鎮座，1944年升格為鄉社，為東石郡的主要神社。戰後曾作為海岸巡防營區使用，社殿遭拆除。1987年軍方撤離後，原址整理為今日的朴子藝術公園。</t>
+  </si>
+  <si>
+    <t>北斗神社</t>
+  </si>
+  <si>
+    <t>北斗家商</t>
+  </si>
+  <si>
+    <t>彰化縣北斗鎮大道里學府路50號</t>
+  </si>
+  <si>
+    <t>北斗神社於1938年落成啟用，1944年升格為鄉社，祭祀開拓三神、明治天皇及北白川宮能久親王。戰後土地由原北斗郡各鄉鎮共同持有，後捐贈政府作教育用途，現址為北斗家商。神社石獅與銅馬等文物則分別保存於其他地點。</t>
+  </si>
+  <si>
+    <t>海山神社</t>
+  </si>
+  <si>
+    <t>員山公園</t>
+  </si>
+  <si>
+    <t>新北市中和區嘉新里員山路455巷</t>
+  </si>
+  <si>
+    <t>海山神社是海山郡社格最高的神社，1938年鎮座，1944年升格為鄉社。其配置完整，並以庇護板橋與中和居民為設計理念。戰後逐漸荒廢並於1950年代遭破壞，目前僅存部分階梯與遺構，後被指定為新北市古蹟。</t>
+  </si>
+  <si>
+    <t>能高神社</t>
+  </si>
+  <si>
+    <t>埔里高工活動中心</t>
+  </si>
+  <si>
+    <t>南投縣埔里鎮枇杷里中山路一段435號</t>
+  </si>
+  <si>
+    <t>能高神社源自埔里地區早期的能高社擴建計畫，歷經多年籌備後於1940年正式鎮座，1944年升格為鄉社。神社規模宏大，擁有完整社殿與附屬設施，是能高郡的重要信仰中心。戰後神社功能終止，原址現為埔里高工活動中心一帶。</t>
+  </si>
+  <si>
+    <t>北門神社</t>
+  </si>
+  <si>
+    <t>佳里公園</t>
+  </si>
+  <si>
+    <t>臺南市佳里區六安里安北路</t>
+  </si>
+  <si>
+    <t>北門神社位於佳里，1936年鎮座，1944年升格為鄉社。當年落成典禮吸引大量官民參與，並舉辦棒球賽與電影放映等活動。戰後神社改建為佳里公園，外苑區域則成為北門高中所在地。</t>
+  </si>
+  <si>
+    <t>南投神社</t>
+  </si>
+  <si>
+    <t>南投高中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南投縣南投市三民里建國路137號</t>
+  </si>
+  <si>
+    <t>南投神社的構想可追溯至日治初期，歷經多次規劃後，新的神社於1943年啟用，並於1944年升格為鄉社。其規模遠大於早期的南投社，是皇民化時期的重要建設。戰後神社不存，現址為南投高中。</t>
+  </si>
+  <si>
+    <t>竹山神社</t>
+  </si>
+  <si>
+    <t>竹山公園</t>
+  </si>
+  <si>
+    <t>南投縣竹山鎮公所路</t>
+  </si>
+  <si>
+    <t>竹山神社於1938年鎮座，1945年升格為鄉社。戰後改作忠烈祠使用，雖然主體建築因921地震受損後拆除，但鳥居、石獅及石燈籠仍獲保存，並於2018年列為南投縣歷史建築。</t>
+  </si>
+  <si>
+    <t>東勢神社</t>
+  </si>
+  <si>
+    <t>東勢高工舊校區</t>
+  </si>
+  <si>
+    <t>臺中市東勢區泰昌里圓樓街1號</t>
+  </si>
+  <si>
+    <t>東勢神社於1937年落成，1945年升格為鄉社，位於東勢市區附近山丘，景觀視野良好。戰後原址設立東勢工業技術講習班，後發展為東勢高工。雖校舍已遷移，舊校區仍保留參道與狛犬等神社遺跡。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -661,6 +806,19 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="BiauKaiTC Regular"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="BiauKaiTC Regular"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -682,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -696,6 +854,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -998,19 +1161,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="10.375" customWidth="1"/>
-    <col min="6" max="6" width="11.375" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="4" width="12.796875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" customWidth="1"/>
+    <col min="6" max="6" width="11.3984375" customWidth="1"/>
+    <col min="7" max="7" width="12.796875" customWidth="1"/>
+    <col min="8" max="8" width="14.59765625" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.2" customHeight="1">
+    <row r="3" spans="1:9" ht="16.25" customHeight="1">
       <c r="A3" s="2">
         <v>102</v>
       </c>
@@ -1097,7 +1260,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.2" customHeight="1">
+    <row r="4" spans="1:9" ht="16.25" customHeight="1">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -1126,7 +1289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.2" customHeight="1">
+    <row r="5" spans="1:9" ht="16.25" customHeight="1">
       <c r="A5" s="2">
         <v>104</v>
       </c>
@@ -1155,7 +1318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.2" customHeight="1">
+    <row r="6" spans="1:9" ht="16.25" customHeight="1">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -1184,7 +1347,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.2" customHeight="1">
+    <row r="7" spans="1:9" ht="16.25" customHeight="1">
       <c r="A7" s="2">
         <v>106</v>
       </c>
@@ -1213,7 +1376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.2" customHeight="1">
+    <row r="8" spans="1:9" ht="16.25" customHeight="1">
       <c r="A8" s="2">
         <v>107</v>
       </c>
@@ -1242,7 +1405,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.2" customHeight="1">
+    <row r="9" spans="1:9" ht="16.25" customHeight="1">
       <c r="A9" s="2">
         <v>108</v>
       </c>
@@ -1271,7 +1434,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.2" customHeight="1">
+    <row r="10" spans="1:9" ht="16.25" customHeight="1">
       <c r="A10" s="2">
         <v>109</v>
       </c>
@@ -1300,7 +1463,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16.2" customHeight="1">
+    <row r="11" spans="1:9" ht="16.25" customHeight="1">
       <c r="A11" s="2">
         <v>110</v>
       </c>
@@ -1329,7 +1492,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.2" customHeight="1">
+    <row r="12" spans="1:9" ht="16.25" customHeight="1">
       <c r="A12" s="2">
         <v>111</v>
       </c>
@@ -1358,7 +1521,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.2" customHeight="1">
+    <row r="13" spans="1:9" ht="16.25" customHeight="1">
       <c r="A13" s="2">
         <v>112</v>
       </c>
@@ -1385,6 +1548,354 @@
       </c>
       <c r="I13" s="2" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" s="2">
+        <v>201</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="10">
+        <v>22.63058146839338</v>
+      </c>
+      <c r="F14" s="10">
+        <v>120.35556131172559</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1935</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" s="2">
+        <v>202</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="10">
+        <v>25.040555494258459</v>
+      </c>
+      <c r="F15" s="10">
+        <v>121.44878398452001</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1937</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" s="2">
+        <v>203</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="10">
+        <v>24.250238689363709</v>
+      </c>
+      <c r="F16" s="10">
+        <v>120.714510849099</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1936</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="2">
+        <v>204</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="10">
+        <v>23.194466086765811</v>
+      </c>
+      <c r="F17" s="10">
+        <v>120.2560588517855</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1938</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="A18" s="2">
+        <v>205</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="10">
+        <v>23.469132960561879</v>
+      </c>
+      <c r="F18" s="10">
+        <v>120.24490809311919</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1936</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="A19" s="2">
+        <v>206</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="10">
+        <v>23.87690369607779</v>
+      </c>
+      <c r="F19" s="10">
+        <v>120.5155049374992</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1938</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="A20" s="2">
+        <v>207</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10">
+        <v>24.998896452047092</v>
+      </c>
+      <c r="F20" s="10">
+        <v>121.4718231305376</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1938</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
+      <c r="A21" s="2">
+        <v>208</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="10">
+        <v>23.975702471983212</v>
+      </c>
+      <c r="F21" s="10">
+        <v>120.97419642855419</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1940</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15">
+      <c r="A22" s="2">
+        <v>209</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="10">
+        <v>23.17071837129852</v>
+      </c>
+      <c r="F22" s="10">
+        <v>120.16998921187501</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1936</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
+      <c r="A23" s="2">
+        <v>210</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="10">
+        <v>23.910518119409129</v>
+      </c>
+      <c r="F23" s="10">
+        <v>120.67264333464369</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1942</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
+      <c r="A24" s="2">
+        <v>211</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="10">
+        <v>23.760506585222849</v>
+      </c>
+      <c r="F24" s="10">
+        <v>120.66165368587821</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1938</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15">
+      <c r="A25" s="2">
+        <v>212</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="10">
+        <v>24.250051973283281</v>
+      </c>
+      <c r="F25" s="10">
+        <v>120.8279283825884</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1937</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1945</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
